--- a/BL4_Legendary_Data.xlsx
+++ b/BL4_Legendary_Data.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Weapons" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Sources" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Class Mods" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Shields" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="Ordnance" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="Repkits" sheetId="6" r:id="rId9"/>
+    <sheet state="visible" name="Weapons" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Sources" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Class Mods" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Shields" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Ordnance" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Repkits" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="778">
   <si>
     <t>Type</t>
   </si>
@@ -48,6 +48,9 @@
     <t>EE</t>
   </si>
   <si>
+    <t>DLC</t>
+  </si>
+  <si>
     <t>Pistol</t>
   </si>
   <si>
@@ -93,6 +96,9 @@
     <t>Windspear, Terminus Range</t>
   </si>
   <si>
+    <t>Dark Subject</t>
+  </si>
+  <si>
     <t>Something's gotta hit.</t>
   </si>
   <si>
@@ -243,6 +249,9 @@
     <t>Hungering Plain, Fadefields</t>
   </si>
   <si>
+    <t>Down and Outbound</t>
+  </si>
+  <si>
     <t>Finish the song!</t>
   </si>
   <si>
@@ -333,7 +342,7 @@
     <t>Trying to paint the prettiest picture I can with the colors I have.</t>
   </si>
   <si>
-    <t>Katagawas Revenge</t>
+    <t>Katagawa's Revenge</t>
   </si>
   <si>
     <t>FS</t>
@@ -417,6 +426,9 @@
     <t>Skyspanner Kratch</t>
   </si>
   <si>
+    <t>Shadow of the Mountain</t>
+  </si>
+  <si>
     <t>All hell can't stop us now.</t>
   </si>
   <si>
@@ -573,9 +585,6 @@
     <t>Stop Gap</t>
   </si>
   <si>
-    <t>FSCR</t>
-  </si>
-  <si>
     <t>The Backhive</t>
   </si>
   <si>
@@ -675,99 +684,102 @@
     <t>Onslaught</t>
   </si>
   <si>
+    <t>Idolator Sol</t>
+  </si>
+  <si>
+    <t>Fortress Indomita, Fadefields</t>
+  </si>
+  <si>
+    <t>Rush the Gate</t>
+  </si>
+  <si>
+    <t>There's a 30% Chance for every bullet fired to deal extra Damage and not consume Ammo.</t>
+  </si>
+  <si>
+    <t>Are ya spinning, son?</t>
+  </si>
+  <si>
+    <t>Are ya winning son meme.</t>
+  </si>
+  <si>
+    <t>Golden God</t>
+  </si>
+  <si>
+    <t>NFC</t>
+  </si>
+  <si>
+    <t>When Overheating, the Bulletforge does not break, but instead continually consumes greater amounts of Ammo.</t>
+  </si>
+  <si>
+    <t>I am untethered, and my rage knows no bounds!</t>
+  </si>
+  <si>
+    <t>Goremaster</t>
+  </si>
+  <si>
+    <t>NFSCR</t>
+  </si>
+  <si>
+    <t>Deals +30% Damage to enemies below 30% Health.</t>
+  </si>
+  <si>
+    <t>"The fact we get to do this for a living is pretty @#%ing cool."</t>
+  </si>
+  <si>
+    <t>Husky Friend</t>
+  </si>
+  <si>
+    <t>NR</t>
+  </si>
+  <si>
+    <t>Primordial Guardian Inceptus</t>
+  </si>
+  <si>
+    <t>Vault of Inceptus, Fadefields</t>
+  </si>
+  <si>
+    <t>Primordial Vault: Fadefields</t>
+  </si>
+  <si>
+    <t>We just prefer to use "Husky".</t>
+  </si>
+  <si>
+    <t>Lead Balloon</t>
+  </si>
+  <si>
+    <t>Splashzone</t>
+  </si>
+  <si>
+    <t>Recruitment Drive</t>
+  </si>
+  <si>
+    <t>Projectiles float upward and spawn child Projectiles upon exploding.</t>
+  </si>
+  <si>
+    <t>For a brick, he flew pretty good.</t>
+  </si>
+  <si>
+    <t>Boomslang</t>
+  </si>
+  <si>
+    <t>Bramblesong</t>
+  </si>
+  <si>
+    <t>Stoneblood Forest, Terminus Range</t>
+  </si>
+  <si>
+    <t>After Reloading, the first Critical Hit Ricochets a Sticky Projectile to up to 3 nearby enemies.</t>
+  </si>
+  <si>
+    <t>Everything is blooming most recklessly.</t>
+  </si>
+  <si>
+    <t>Convergence</t>
+  </si>
+  <si>
     <t>RY</t>
   </si>
   <si>
-    <t>Idolator Sol</t>
-  </si>
-  <si>
-    <t>Fortress Indomita, Fadefields</t>
-  </si>
-  <si>
-    <t>There's a 30% Chance for every bullet fired to deal extra Damage and not consume Ammo.</t>
-  </si>
-  <si>
-    <t>Are ya spinning, son?</t>
-  </si>
-  <si>
-    <t>Are ya winning son meme.</t>
-  </si>
-  <si>
-    <t>Golden God</t>
-  </si>
-  <si>
-    <t>NFC</t>
-  </si>
-  <si>
-    <t>When Overheating, the Bulletforge does not break, but instead continually consumes greater amounts of Ammo.</t>
-  </si>
-  <si>
-    <t>I am untethered, and my rage knows no bounds!</t>
-  </si>
-  <si>
-    <t>Goremaster</t>
-  </si>
-  <si>
-    <t>NFSR</t>
-  </si>
-  <si>
-    <t>Deals +30% Damage to enemies below 30% Health.</t>
-  </si>
-  <si>
-    <t>"The fact we get to do this for a living is pretty @#%ing cool."</t>
-  </si>
-  <si>
-    <t>Husky Friend</t>
-  </si>
-  <si>
-    <t>NR</t>
-  </si>
-  <si>
-    <t>Primordial Guardian Inceptus</t>
-  </si>
-  <si>
-    <t>Vault of Inceptus, Fadefields</t>
-  </si>
-  <si>
-    <t>Primordial Vault: Fadefields</t>
-  </si>
-  <si>
-    <t>We just prefer to use "Husky".</t>
-  </si>
-  <si>
-    <t>Lead Balloon</t>
-  </si>
-  <si>
-    <t>Splashzone</t>
-  </si>
-  <si>
-    <t>Recruitment Drive</t>
-  </si>
-  <si>
-    <t>Projectiles float upward and spawn child Projectiles upon exploding.</t>
-  </si>
-  <si>
-    <t>For a brick, he flew pretty good.</t>
-  </si>
-  <si>
-    <t>Boomslang</t>
-  </si>
-  <si>
-    <t>Bramblesong</t>
-  </si>
-  <si>
-    <t>Stoneblood Forest, Terminus Range</t>
-  </si>
-  <si>
-    <t>After Reloading, the first Critical Hit Ricochets a Sticky Projectile to up to 3 nearby enemies.</t>
-  </si>
-  <si>
-    <t>Everything is blooming most recklessly.</t>
-  </si>
-  <si>
-    <t>Convergence</t>
-  </si>
-  <si>
     <t>Steel chambers, late the pyres; Of her salamandrine fires.</t>
   </si>
   <si>
@@ -933,6 +945,9 @@
     <t>Anarchy</t>
   </si>
   <si>
+    <t>NFSCY</t>
+  </si>
+  <si>
     <t>Primordial Guardian Radix</t>
   </si>
   <si>
@@ -993,6 +1008,9 @@
     <t>Moxxi Tip Jar</t>
   </si>
   <si>
+    <t>Wrath of the Ripper Queen</t>
+  </si>
+  <si>
     <t>You've been smooching with everybody.</t>
   </si>
   <si>
@@ -1032,6 +1050,366 @@
     <t>Developer voted name.</t>
   </si>
   <si>
+    <t>Inscriber</t>
+  </si>
+  <si>
+    <t>Minister Screw</t>
+  </si>
+  <si>
+    <t>Ministry of Culture, Fadefields</t>
+  </si>
+  <si>
+    <t>The War On Mercenary Day</t>
+  </si>
+  <si>
+    <t>Hitting enemies spawns 4 projectiles behind them.</t>
+  </si>
+  <si>
+    <t>For those who come after.</t>
+  </si>
+  <si>
+    <t>Rowdy Rider</t>
+  </si>
+  <si>
+    <t>+2 Ricochet Projectiles on Critical Hits</t>
+  </si>
+  <si>
+    <t>Plink, headshot.</t>
+  </si>
+  <si>
+    <t>Aching Roil</t>
+  </si>
+  <si>
+    <t>Vault Card 1</t>
+  </si>
+  <si>
+    <t>Overheating prevents firing. Switching modes reduces heat.</t>
+  </si>
+  <si>
+    <t>Sleep down in the soil.</t>
+  </si>
+  <si>
+    <t>Rooker</t>
+  </si>
+  <si>
+    <t>Fires 2 Needles that continuously home in on enemies you are aiming at.</t>
+  </si>
+  <si>
+    <t>For daddies, not fathers.</t>
+  </si>
+  <si>
+    <t>Hardpoint</t>
+  </si>
+  <si>
+    <t>Hope your core's armored.</t>
+  </si>
+  <si>
+    <t>Missilaser</t>
+  </si>
+  <si>
+    <t>Underbarrel fires sticky rockets. Main barrel fires a laser that detonates attached rockets each dealing some damage.</t>
+  </si>
+  <si>
+    <t>Paint the target!</t>
+  </si>
+  <si>
+    <t>Laser-Cutter</t>
+  </si>
+  <si>
+    <t>CY</t>
+  </si>
+  <si>
+    <t>Corporal Brennan</t>
+  </si>
+  <si>
+    <t>Crooked Teeth, The Whispering Glacier</t>
+  </si>
+  <si>
+    <t>Hearing Things</t>
+  </si>
+  <si>
+    <t>Isaac's bestie.</t>
+  </si>
+  <si>
+    <t>Mad Ellie</t>
+  </si>
+  <si>
+    <t>Scoot'n'Shoot</t>
+  </si>
+  <si>
+    <t>Crazed Earl</t>
+  </si>
+  <si>
+    <t>Bloodstained Hollow, The Whispering Glacier</t>
+  </si>
+  <si>
+    <t>It Grows Below</t>
+  </si>
+  <si>
+    <t>Phantom Guns fire from the locations of your previous shots. Phantom Guns reset on reload.</t>
+  </si>
+  <si>
+    <t>Move it or lose it!</t>
+  </si>
+  <si>
+    <t>Reminisce</t>
+  </si>
+  <si>
+    <t>SCRY</t>
+  </si>
+  <si>
+    <t>Captain Willis</t>
+  </si>
+  <si>
+    <t>Vault of the Damned, The Whispering Glacier</t>
+  </si>
+  <si>
+    <t>Damnation Encroaches</t>
+  </si>
+  <si>
+    <t>Does not reload, and instead refills Ammo when the projectiles return.</t>
+  </si>
+  <si>
+    <t>What goes around...</t>
+  </si>
+  <si>
+    <t>Hemorrhage</t>
+  </si>
+  <si>
+    <t>Colonel Crash</t>
+  </si>
+  <si>
+    <t>DCN Feuermann, The Whispering Glacier</t>
+  </si>
+  <si>
+    <t>What Lies Dreaming</t>
+  </si>
+  <si>
+    <t>Deals increased Damage the farther away the target is.</t>
+  </si>
+  <si>
+    <t>Stay back, I have powers.</t>
+  </si>
+  <si>
+    <t>Flash Cyclone</t>
+  </si>
+  <si>
+    <t>The Penitent Steel</t>
+  </si>
+  <si>
+    <t>Windswept Wastes, The Whispering Glacier</t>
+  </si>
+  <si>
+    <t>DAHL Bunker</t>
+  </si>
+  <si>
+    <t>Chance on Hit to Explode and Spawn additional projectiles.</t>
+  </si>
+  <si>
+    <t>What cyclone? Its a couple of flakes!</t>
+  </si>
+  <si>
+    <t>Prowler</t>
+  </si>
+  <si>
+    <t>Air Raider Scremulous</t>
+  </si>
+  <si>
+    <t>Fuel Siphon</t>
+  </si>
+  <si>
+    <t>Bullets slowly home in on targets. Reloading accelerates them toward their targets.</t>
+  </si>
+  <si>
+    <t>Nope.</t>
+  </si>
+  <si>
+    <t>Sunspot</t>
+  </si>
+  <si>
+    <t>Big Oil</t>
+  </si>
+  <si>
+    <t>Damage scales based on the emptiness of the Magazine.</t>
+  </si>
+  <si>
+    <t>Sun Spot! Sun Spot run! Run Spot run!</t>
+  </si>
+  <si>
+    <t>Fearstalker</t>
+  </si>
+  <si>
+    <t>Nightmare Rift Bosses</t>
+  </si>
+  <si>
+    <t>The Whispering Glacier</t>
+  </si>
+  <si>
+    <t>Nightmare Rifts</t>
+  </si>
+  <si>
+    <t>Critical Hits grant a Stack of Deduction that increases the next Non-Critical Hit Damage by +200% per Stack. Non-Critical Hits grant a Stack of Observation that increases the next Critical Hit Damage by +100% per Stack.</t>
+  </si>
+  <si>
+    <t>Quite right...mauled to death it seems.</t>
+  </si>
+  <si>
+    <t>Falke</t>
+  </si>
+  <si>
+    <t>Let us become whole again.</t>
+  </si>
+  <si>
+    <t>Kor</t>
+  </si>
+  <si>
+    <t>Detonating Stickies triggers a Nova. Nova Damage scales with the number of attached Stickies.</t>
+  </si>
+  <si>
+    <t>It's building up, building up, building deep inside.</t>
+  </si>
+  <si>
+    <t>Bubbles</t>
+  </si>
+  <si>
+    <t>CRY</t>
+  </si>
+  <si>
+    <t>Chiselbella</t>
+  </si>
+  <si>
+    <t>The Demon's Domain</t>
+  </si>
+  <si>
+    <t>The Cursed Mine</t>
+  </si>
+  <si>
+    <t>So sassy.</t>
+  </si>
+  <si>
+    <t>Bounty Pack 2</t>
+  </si>
+  <si>
+    <t>Mercurious</t>
+  </si>
+  <si>
+    <t>Bullet Damage scales with Movement Speed.</t>
+  </si>
+  <si>
+    <t>The mighty giant-killer, stood there, spellbound.</t>
+  </si>
+  <si>
+    <t>Doeshot</t>
+  </si>
+  <si>
+    <t>Bore-Tex</t>
+  </si>
+  <si>
+    <t>So La Ti Buck</t>
+  </si>
+  <si>
+    <t>Roulette</t>
+  </si>
+  <si>
+    <t>On Reload, gain random buffs.</t>
+  </si>
+  <si>
+    <t>Papa needs a new pair of class mods!</t>
+  </si>
+  <si>
+    <t>Laser Disker</t>
+  </si>
+  <si>
+    <t>FSY</t>
+  </si>
+  <si>
+    <t>Sturmdrang</t>
+  </si>
+  <si>
+    <t>Deals 200% Damage to airborne enemies.</t>
+  </si>
+  <si>
+    <t>A U.F.O. is just an I.F.O. you haven't met.</t>
+  </si>
+  <si>
+    <t>Hair Trigger</t>
+  </si>
+  <si>
+    <t>NSC</t>
+  </si>
+  <si>
+    <t>Projectiles explode when releasing the trigger.</t>
+  </si>
+  <si>
+    <t>You're going to regret this for the rest of your life...</t>
+  </si>
+  <si>
+    <t>Broken Wings</t>
+  </si>
+  <si>
+    <t>Stone Demon</t>
+  </si>
+  <si>
+    <t>It's a sprint, not a marathon.</t>
+  </si>
+  <si>
+    <t>Fleabag</t>
+  </si>
+  <si>
+    <t>NSCY</t>
+  </si>
+  <si>
+    <t>Sticky Projectiles move to the most recently hit target.</t>
+  </si>
+  <si>
+    <t>Can't you see the fleas?</t>
+  </si>
+  <si>
+    <t>Shalashaska</t>
+  </si>
+  <si>
+    <t>Ordonite Processor</t>
+  </si>
+  <si>
+    <t>Lopside, Carcadia Burn | Cuspid Climb, Terminus Range | The Howl, Fadefields | The Demon's Domain</t>
+  </si>
+  <si>
+    <t>On Auto-Reload, grants a Stack of Exhiliration. Each stack of Exhiliration increases the number of possible Ricochets by 1. Resets on manual Reload.</t>
+  </si>
+  <si>
+    <t>I love to reload during a battle.</t>
+  </si>
+  <si>
+    <t>Reference to Revolver Ocelot in Metal Gear Solid</t>
+  </si>
+  <si>
+    <t>Rainmaker</t>
+  </si>
+  <si>
+    <t>Bloomreaper the Invincible</t>
+  </si>
+  <si>
+    <t>The Bloom</t>
+  </si>
+  <si>
+    <t>The Wrath of Bloomreaper</t>
+  </si>
+  <si>
+    <t>Drown in lead.</t>
+  </si>
+  <si>
+    <t>Mantra</t>
+  </si>
+  <si>
+    <t>FSCY</t>
+  </si>
+  <si>
+    <t>Deals Melee damage.</t>
+  </si>
+  <si>
+    <t>Punch your way to self-actualization</t>
+  </si>
+  <si>
     <t>Fractis</t>
   </si>
   <si>
@@ -1272,6 +1650,135 @@
     <t>Our nature is to fly.</t>
   </si>
   <si>
+    <t>Configuration</t>
+  </si>
+  <si>
+    <t>When Vex activates an Action Skill or Command Skill open a Blood Rift for a duration. Maximum of 2 active Blood Rifts at a time. Blood Rifts rapidly fire Remnant Minions, dealing Kinetic Gun Damage based on her Current Weapon when spawned.</t>
+  </si>
+  <si>
+    <t>No need to waste such sweet suffering.</t>
+  </si>
+  <si>
+    <t>Phlebotomist</t>
+  </si>
+  <si>
+    <t>While Harlowe's Action Skill is active, dealing Gun Damage to an enemy has a chance to cause a Hemorrhage, dealing Kinetic Status Effect Damage based on Damage Dealt. Hemorrhage deals twice as much Damage to Bosses.</t>
+  </si>
+  <si>
+    <t>Be the reason someone gets a second death.</t>
+  </si>
+  <si>
+    <t>Tempest</t>
+  </si>
+  <si>
+    <t>Dealing Gun Damage grants Storm for 20 seconds, increasing Shock Damage, stacking up to 50 times. Activating a Forgeskill causes Elemental Bolts to strike random nearby enemies for 10 seconds, dealing Shock Skill Damage based on Maximum Shield Capacity.</t>
+  </si>
+  <si>
+    <t>Hell is empty and all the devils are here.</t>
+  </si>
+  <si>
+    <t>Rogue</t>
+  </si>
+  <si>
+    <t>Cooler</t>
+  </si>
+  <si>
+    <t>Whenever C4SH deals Ordnance Damage to an enemy, that enemy becomes Jinxed. Whenever C4SH kills a Jinxed enemy, he gains +20% Ordnance Cooldown Rate for 12 seconds. This effect stacks up to 10 times.</t>
+  </si>
+  <si>
+    <t>Do do that voodoo that you do so well.</t>
+  </si>
+  <si>
+    <t>Hooligan</t>
+  </si>
+  <si>
+    <t>Whenever C4SH kills an enemy, gain a stack of Hooligan. Whenever C4SH deals Grenade Damage, consume all Hooligan Stacks and deal +40% Bonus Fire Damage per Stack. If Windfall is active, only consume half of the Stacks. C4SH can have up to 25 Hooligan Stacks.</t>
+  </si>
+  <si>
+    <t>Here we go, here we go, here we go!</t>
+  </si>
+  <si>
+    <t>Ludopath</t>
+  </si>
+  <si>
+    <t>Whenever C4SH rolls his Bone Dice, he gains Ludopath Stacks equal to the roll. C4SH gains +3% Fire Rate and +5% Movement Speed for every Ludopath Stack. C4SH has a Max of 36 Ludopath Stacks and each Stack lasts for 12 seconds.</t>
+  </si>
+  <si>
+    <t>They see me rollin'</t>
+  </si>
+  <si>
+    <t>Hotshot</t>
+  </si>
+  <si>
+    <t>Cross-Fire's Burst Fire is replaced with a Beam Spin Attack that deals Fire Damage. If Windfall is active, these Beams always Critically Hit enemies.</t>
+  </si>
+  <si>
+    <t>Spin to win</t>
+  </si>
+  <si>
+    <t>Gamer</t>
+  </si>
+  <si>
+    <t>Whenever C4SH Critically Hits an enemy with a Gun, Bleed that enemy. Whenever C4SH kills an enemy with Bleed with a Critical Hit, he gains a 7% Chance to spawn a Chaos Totem. While Windfall is active, double that Chance.</t>
+  </si>
+  <si>
+    <t>Luck is what happens when preparation meets opportunity.</t>
+  </si>
+  <si>
+    <t>Windrider</t>
+  </si>
+  <si>
+    <t>Whenever C4SH kills an enemy with a Critical Hit from a Gun, he doubles his Fortune Stacks, otherwise killing an enemy with a Gun drains half of C4SH's Fortune Stacks. Whenever C4SH gains Fortune, he restores 5% of his Maximum Health. Whenever C4SH loses Fortune, he gains 8% of his Max Overshield.</t>
+  </si>
+  <si>
+    <t>Play to win. Never play to not lose.</t>
+  </si>
+  <si>
+    <t>Rounder</t>
+  </si>
+  <si>
+    <t>Sleight of Hand gains Reduced Charges. Whenever C4SH kills an enemy with a Card, he gains 2 Charges and resets his Action Skill Duration.</t>
+  </si>
+  <si>
+    <t>And for my next trick...</t>
+  </si>
+  <si>
+    <t>Overdriver</t>
+  </si>
+  <si>
+    <t>Rafa deals increased Ordnance and Gun Damage the faster he moves. While Overdrive is active, this bonus is doubled.</t>
+  </si>
+  <si>
+    <t>Rapido corren los carros cargados.</t>
+  </si>
+  <si>
+    <t>Trooper</t>
+  </si>
+  <si>
+    <t>Critical Hits with Guns partially restore Ordnance Cooldown. On Ordnance Activation, gain Gun Damage and Action Skill Damage for a Duration.</t>
+  </si>
+  <si>
+    <t>I'm doing my part!</t>
+  </si>
+  <si>
+    <t>Lamplighter</t>
+  </si>
+  <si>
+    <t>Whenever Amon Critically Hits with Guns, he partially restores Action Skill Duration. While Action Skill is active, he gains increased Gun and Melee Damage every second until Action Skill ends.</t>
+  </si>
+  <si>
+    <t>No need of sun to light the way.</t>
+  </si>
+  <si>
+    <t>Whale</t>
+  </si>
+  <si>
+    <t>C4SH's Action Skill Cooldown Rate is reduced to 0 and all Action Skill Cooldown Rate bonuses are converted into Action Skill Damage. Whenever he gains a Stack of Fortune, he restores 10% of his Action Skill Cooldown, gains +20% Fire Rate, and +25% Reload Speed for 8 seconds.</t>
+  </si>
+  <si>
+    <t>I have not yet begun to defile myself.</t>
+  </si>
+  <si>
     <t>Energy</t>
   </si>
   <si>
@@ -1287,6 +1794,9 @@
     <t>Pandoran Memento</t>
   </si>
   <si>
+    <t>NFSCRY</t>
+  </si>
+  <si>
     <t>When Damaged, grants +15% Elemental Resistance and +50% Resistance to the last Damage Type received for 5s.</t>
   </si>
   <si>
@@ -1299,9 +1809,6 @@
     <t>Guardian Angel</t>
   </si>
   <si>
-    <t>SCR</t>
-  </si>
-  <si>
     <t>When equipped, grants faster revival from Fight for Your Life. When FFYL expires, grants 1 free Second Wind once every 300s.</t>
   </si>
   <si>
@@ -1314,90 +1821,84 @@
     <t>Cindershelly</t>
   </si>
   <si>
+    <t>NFSRY</t>
+  </si>
+  <si>
+    <t>When Damaged, grants a Stack of Resolve - which reduced Damage Taken by 2% per Stack - for up to 25 Stacks. When the Shield breaks, release a Nova dealing damage, with each Stack of Resolve increasing the damage by +20%.</t>
+  </si>
+  <si>
+    <t>Skip to the end</t>
+  </si>
+  <si>
+    <t>Cinderella Shoes</t>
+  </si>
+  <si>
+    <t>Protean Cell</t>
+  </si>
+  <si>
+    <t>Ground Slam to toggle this effect. While enabled, drains Shield over time to grant +40% Bonus Shock Damage, and Damage Taken passes through the Shield.</t>
+  </si>
+  <si>
+    <t>Electrical resistance is futile.</t>
+  </si>
+  <si>
+    <t>Extra Medium</t>
+  </si>
+  <si>
+    <t>When Energy Shield breaks or fills, it triggers a Nova that deals Damage.</t>
+  </si>
+  <si>
+    <t>Never above five on the call sheet of life..</t>
+  </si>
+  <si>
+    <t>Meat Cooking</t>
+  </si>
+  <si>
+    <t>Super Soldier</t>
+  </si>
+  <si>
+    <t>When Energy Shield fills, grants an Overshield. When Energy Shield is full, grants 25% Fire Rate, 25% Movement Speed, and regens 1 Ammo/s</t>
+  </si>
+  <si>
+    <t>I'll never forget the adventures we had.</t>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>Emollient Hoarder</t>
+  </si>
+  <si>
+    <t>On kill, 50% Chance to spawn an Ammo Booster that instantly refills your Gun.</t>
+  </si>
+  <si>
+    <t>BYO bullets!</t>
+  </si>
+  <si>
+    <t>Marcus vendor quote</t>
+  </si>
+  <si>
+    <t>Timekeeper's New Shield</t>
+  </si>
+  <si>
+    <t>The Timekeeper | Primordial Guardian Timekeeper</t>
+  </si>
+  <si>
+    <t>When equipped, increases Maximum Health, grants additional Health Regeneration per second, and reduces Damage Taken by 33%.</t>
+  </si>
+  <si>
+    <t>It's all coming together.</t>
+  </si>
+  <si>
+    <t>The Emperor's New Groove</t>
+  </si>
+  <si>
+    <t>Heavyweight</t>
+  </si>
+  <si>
     <t>NSRY</t>
   </si>
   <si>
-    <t>When Damaged, grants a Stack of Resolve - which reduced Damage Taken by 2% per Stack - for up to 25 Stacks. When the Shield breaks, release a Nova dealing damage, with each Stack of Resolve increasing the damage by +20%.</t>
-  </si>
-  <si>
-    <t>Skip to the end</t>
-  </si>
-  <si>
-    <t>Cinderella Shoes</t>
-  </si>
-  <si>
-    <t>Protean Cell</t>
-  </si>
-  <si>
-    <t>Ground Slam to toggle this effect. While enabled, drains Shield over time to grant +40% Bonus Shock Damage, and Damage Taken passes through the Shield.</t>
-  </si>
-  <si>
-    <t>Electrical resistance is futile.</t>
-  </si>
-  <si>
-    <t>Extra Medium</t>
-  </si>
-  <si>
-    <t>NFSRY</t>
-  </si>
-  <si>
-    <t>When Energy Shield breaks or fills, it triggers a Nova that deals Damage.</t>
-  </si>
-  <si>
-    <t>Never above five on the call sheet of life..</t>
-  </si>
-  <si>
-    <t>Meat Cooking</t>
-  </si>
-  <si>
-    <t>Super Soldier</t>
-  </si>
-  <si>
-    <t>NFSCR</t>
-  </si>
-  <si>
-    <t>When Energy Shield fills, grants an Overshield. When Energy Shield is full, grants 25% Fire Rate, 25% Movement Speed, and regens 1 Ammo/s</t>
-  </si>
-  <si>
-    <t>I'll never forget the adventures we had.</t>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <t>Emollient Hoarder</t>
-  </si>
-  <si>
-    <t>CRY</t>
-  </si>
-  <si>
-    <t>On kill, 50% Chance to spawn an Ammo Booster that instantly refills your Gun.</t>
-  </si>
-  <si>
-    <t>BYO bullets!</t>
-  </si>
-  <si>
-    <t>Marcus vendor quote</t>
-  </si>
-  <si>
-    <t>Timekeeper's New Shield</t>
-  </si>
-  <si>
-    <t>The Timekeeper | Primordial Guardian Timekeeper</t>
-  </si>
-  <si>
-    <t>When equipped, increases Maximum Health, grants additional Health Regeneration per second, and reduces Damage Taken by 33%.</t>
-  </si>
-  <si>
-    <t>It's all coming together.</t>
-  </si>
-  <si>
-    <t>The Emperor's New Groove</t>
-  </si>
-  <si>
-    <t>Heavyweight</t>
-  </si>
-  <si>
     <t>On Melee Hit, consumes an Armor Segment to grant +100% Melee Damage. When Armor Shield is empty, grants +50% Melee Damage.</t>
   </si>
   <si>
@@ -1428,9 +1929,6 @@
     <t>Onion</t>
   </si>
   <si>
-    <t>NSC</t>
-  </si>
-  <si>
     <t>On Armor Segment break, grants Immunity to Damage for 2s.</t>
   </si>
   <si>
@@ -1464,6 +1962,39 @@
     <t>Protect me, squire!</t>
   </si>
   <si>
+    <t>Elpis Star</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>When dealing Melee Damage, spawn a Meteor Cluster to fall on the damaged enemy.</t>
+  </si>
+  <si>
+    <t>Make a wish.</t>
+  </si>
+  <si>
+    <t>Hopscotch</t>
+  </si>
+  <si>
+    <t>Spawns a Singularity when an Armor Segment breaks.</t>
+  </si>
+  <si>
+    <t>I kept you hopping didn't I?</t>
+  </si>
+  <si>
+    <t>Undershield</t>
+  </si>
+  <si>
+    <t>NSY</t>
+  </si>
+  <si>
+    <t>On Armor Segment break, grants Overshield.</t>
+  </si>
+  <si>
+    <t>Anything worth doing is worth doing in excess.</t>
+  </si>
+  <si>
     <t>Grenade</t>
   </si>
   <si>
@@ -1500,9 +2031,6 @@
     <t>Fuse</t>
   </si>
   <si>
-    <t>NSCRY</t>
-  </si>
-  <si>
     <t>Who you calling short?!</t>
   </si>
   <si>
@@ -1557,9 +2085,6 @@
     <t>Recursive</t>
   </si>
   <si>
-    <t>FSY</t>
-  </si>
-  <si>
     <t>Let's do this, one last time...</t>
   </si>
   <si>
@@ -1608,9 +2133,6 @@
     <t>Buoy</t>
   </si>
   <si>
-    <t>CY</t>
-  </si>
-  <si>
     <t>No wake zone...</t>
   </si>
   <si>
@@ -1647,9 +2169,6 @@
     <t>Tinged Inkling</t>
   </si>
   <si>
-    <t>FSCY</t>
-  </si>
-  <si>
     <t>Fires bouncing Projectiles that leave an Elemental Splat on bounce.</t>
   </si>
   <si>
@@ -1668,9 +2187,6 @@
     <t>Blockbuster</t>
   </si>
   <si>
-    <t>NFSCRY</t>
-  </si>
-  <si>
     <t>They don't make 'em like this anymore.</t>
   </si>
   <si>
@@ -1683,15 +2199,60 @@
     <t>Gamma Void</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>Creates a Singularity for 10s, in which enemies take +40% Radiation Damage over time.</t>
   </si>
   <si>
     <t>Dwell not in the inner void.</t>
   </si>
   <si>
+    <t>Bismuth-Tipped Dagger</t>
+  </si>
+  <si>
+    <t>FY</t>
+  </si>
+  <si>
+    <t>Attaches on Hit. Enemies take 15% more Cryo damage for each attached Dagger.</t>
+  </si>
+  <si>
+    <t>Get down with the Bismuth!</t>
+  </si>
+  <si>
+    <t>Barb'ara</t>
+  </si>
+  <si>
+    <t>Ooh, mami.</t>
+  </si>
+  <si>
+    <t>Heimdahl</t>
+  </si>
+  <si>
+    <t>NCR</t>
+  </si>
+  <si>
+    <t>Fires Dahl soldier heads that attack nearby enemies.</t>
+  </si>
+  <si>
+    <t>In his eternal service.</t>
+  </si>
+  <si>
+    <t>Ichor</t>
+  </si>
+  <si>
+    <t>Deals Incendiary and Corrosive Damage.</t>
+  </si>
+  <si>
+    <t>Their excellence already bursting from their fingertips.</t>
+  </si>
+  <si>
+    <t>Urchin</t>
+  </si>
+  <si>
+    <t>Benthic boogie.</t>
+  </si>
+  <si>
+    <t>Jetsetter</t>
+  </si>
+  <si>
     <t>Augmenter AF1000</t>
   </si>
   <si>
@@ -1762,6 +2323,33 @@
   </si>
   <si>
     <t>I'm curious about that myself.</t>
+  </si>
+  <si>
+    <t>Healthraiser</t>
+  </si>
+  <si>
+    <t>Spawns Health Boosters at the start and end of the Repkit's duration.</t>
+  </si>
+  <si>
+    <t>No tears, please.</t>
+  </si>
+  <si>
+    <t>Blood Moon</t>
+  </si>
+  <si>
+    <t>Heals for the last 5 instances of Damage taken within the last 4 seconds.</t>
+  </si>
+  <si>
+    <t>Fighting evil by moonlight.</t>
+  </si>
+  <si>
+    <t>Geiger-Roid</t>
+  </si>
+  <si>
+    <t>On Use applies 5 stacks of Roid-Rage that decay over time. Each time a stack expires spawn an elemental Nova (can roll any single element) dealing damage.</t>
+  </si>
+  <si>
+    <t>This is the part where you run.</t>
   </si>
 </sst>
 </file>
@@ -1787,18 +2375,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1823,8 +2405,12 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1855,6 +2441,10 @@
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2062,7 +2652,7 @@
     <col customWidth="1" min="3" max="3" width="11.5"/>
     <col customWidth="1" min="4" max="4" width="8.5"/>
     <col customWidth="1" min="5" max="5" width="21.88"/>
-    <col customWidth="1" min="6" max="6" width="31.0"/>
+    <col customWidth="1" min="6" max="6" width="34.5"/>
     <col customWidth="1" min="7" max="7" width="21.38"/>
     <col customWidth="1" min="8" max="8" width="61.5"/>
     <col customWidth="1" min="9" max="9" width="46.5"/>
@@ -2100,2173 +2690,3095 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="3"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>11</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" s="4"/>
+        <v>34</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>39</v>
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>11</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K7" s="4"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>93</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>95</v>
+        <v>54</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K15" s="3"/>
+        <v>102</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>100</v>
+        <v>79</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>105</v>
+        <v>86</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="K17" s="4"/>
+        <v>114</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="4"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="K19" s="3"/>
+        <v>124</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="G20" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="K20" s="4"/>
+        <v>129</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>127</v>
+        <v>86</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K21" s="3"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>134</v>
+        <v>79</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>138</v>
+        <v>54</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>142</v>
+        <v>79</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K25" s="4"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>145</v>
+        <v>79</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>149</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>148</v>
+        <v>79</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>150</v>
+        <v>54</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>154</v>
+        <v>119</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>158</v>
+        <v>119</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>160</v>
+        <v>79</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>163</v>
+        <v>11</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K32" s="4"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>166</v>
+        <v>54</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K33" s="3"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>172</v>
+        <v>119</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>178</v>
+        <v>11</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>184</v>
+        <v>86</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K36" s="3"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>190</v>
+        <v>119</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K37" s="3"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>193</v>
+        <v>86</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>199</v>
+        <v>54</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>204</v>
+        <v>11</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>209</v>
+        <v>11</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>212</v>
+        <v>11</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>215</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>215</v>
+        <v>54</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>218</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>218</v>
+        <v>119</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>221</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>219</v>
+        <v>23</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>225</v>
+        <v>79</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>228</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>229</v>
+        <v>79</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>233</v>
+        <v>79</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>236</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>239</v>
+        <v>79</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>244</v>
+        <v>86</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B50" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="G50" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>251</v>
+        <v>54</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>255</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>255</v>
+        <v>86</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>259</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>259</v>
+        <v>11</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>263</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>264</v>
+        <v>11</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>270</v>
+        <v>119</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>276</v>
+        <v>79</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>280</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>281</v>
+        <v>79</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>285</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="F58" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>289</v>
+        <v>54</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>293</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>292</v>
+        <v>86</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>296</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>297</v>
+        <v>119</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>301</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>304</v>
+        <v>79</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>308</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>310</v>
+        <v>86</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>315</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>313</v>
+        <v>54</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>318</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>316</v>
+        <v>79</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>321</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>319</v>
+        <v>86</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>324</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>322</v>
+        <v>54</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>327</v>
+        <v>79</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>333</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4296,450 +5808,576 @@
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>102</v>
+      <c r="A9" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>338</v>
+        <v>464</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>73</v>
+      <c r="A16" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>220</v>
+      <c r="A17" s="3" t="s">
+        <v>222</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>46</v>
+      <c r="A24" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>272</v>
+      <c r="A25" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="s">
-        <v>305</v>
+      <c r="A26" s="3" t="s">
+        <v>310</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="s">
-        <v>260</v>
+      <c r="A37" s="3" t="s">
+        <v>264</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="s">
-        <v>195</v>
+      <c r="A38" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -4763,7 +6401,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>465</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4781,7 +6419,7 @@
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>340</v>
+        <v>466</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
@@ -4789,620 +6427,976 @@
       <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>342</v>
+        <v>467</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>468</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>343</v>
+        <v>469</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>344</v>
+        <v>470</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>346</v>
+        <v>471</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>472</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>347</v>
+        <v>473</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>348</v>
+        <v>474</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>350</v>
+        <v>475</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>476</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>351</v>
+        <v>477</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>352</v>
+        <v>478</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>353</v>
+        <v>475</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>479</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>354</v>
+        <v>480</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>355</v>
+        <v>481</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>356</v>
+        <v>471</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>482</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>357</v>
+        <v>483</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>358</v>
+        <v>484</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>359</v>
+        <v>475</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>485</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>360</v>
+        <v>486</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>361</v>
+        <v>487</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>363</v>
+        <v>488</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>489</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>364</v>
+        <v>490</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>365</v>
+        <v>491</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>365</v>
+        <v>491</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>366</v>
+        <v>475</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>492</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>367</v>
+        <v>493</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>368</v>
+        <v>494</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>369</v>
+        <v>495</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>370</v>
+        <v>471</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>496</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>371</v>
+        <v>497</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>372</v>
+        <v>498</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>373</v>
+        <v>467</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>499</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>374</v>
+        <v>500</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>375</v>
+        <v>501</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>376</v>
+        <v>467</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>502</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>377</v>
+        <v>503</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>378</v>
+        <v>504</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>379</v>
+        <v>471</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>505</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>380</v>
+        <v>506</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>381</v>
+        <v>507</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>382</v>
+        <v>488</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>508</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>383</v>
+        <v>509</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>384</v>
+        <v>510</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>385</v>
+        <v>488</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>511</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>386</v>
+        <v>512</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>387</v>
+        <v>513</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>388</v>
+        <v>467</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>514</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>389</v>
+        <v>515</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>390</v>
+        <v>516</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>391</v>
+        <v>471</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>517</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>392</v>
+        <v>518</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>393</v>
+        <v>519</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>394</v>
+        <v>475</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>520</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>395</v>
+        <v>521</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>396</v>
+        <v>522</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>397</v>
+        <v>467</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>523</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>398</v>
+        <v>524</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>399</v>
+        <v>525</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>400</v>
+        <v>471</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>526</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>401</v>
+        <v>527</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>402</v>
+        <v>528</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>403</v>
+        <v>475</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>529</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>404</v>
+        <v>530</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>405</v>
+        <v>531</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>406</v>
+        <v>488</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>532</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>407</v>
+        <v>533</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>408</v>
+        <v>534</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>409</v>
+        <v>467</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>535</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>410</v>
+        <v>536</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>411</v>
+        <v>537</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>412</v>
+        <v>488</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>538</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>413</v>
+        <v>539</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>414</v>
+        <v>540</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>415</v>
+        <v>488</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>541</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>416</v>
+        <v>542</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>417</v>
+        <v>543</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -5459,511 +7453,619 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>419</v>
+        <v>587</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>588</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>420</v>
+        <v>589</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>421</v>
+        <v>590</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>422</v>
+        <v>587</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>591</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>230</v>
+        <v>592</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>423</v>
+        <v>593</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>424</v>
+        <v>594</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>425</v>
+        <v>595</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>426</v>
+        <v>587</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>596</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>427</v>
+        <v>592</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>428</v>
+        <v>597</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>429</v>
+        <v>598</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>430</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>431</v>
+        <v>587</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>600</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>432</v>
+        <v>601</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>433</v>
+        <v>602</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>434</v>
+        <v>603</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>435</v>
+        <v>604</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>436</v>
+        <v>587</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>605</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>338</v>
+        <v>464</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>437</v>
+        <v>606</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>438</v>
+        <v>607</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="4"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>439</v>
+        <v>587</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>608</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>440</v>
+        <v>592</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>441</v>
+        <v>609</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>442</v>
+        <v>610</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>443</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>444</v>
+        <v>587</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>612</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>445</v>
+        <v>233</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>446</v>
+        <v>613</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>447</v>
+        <v>614</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>449</v>
+        <v>615</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>616</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>450</v>
+        <v>418</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="H9" s="2" t="s">
-        <v>451</v>
+        <v>617</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>452</v>
+        <v>618</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>453</v>
+        <v>619</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>454</v>
+        <v>615</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>620</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>455</v>
+        <v>621</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>456</v>
+        <v>622</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>457</v>
+        <v>623</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>458</v>
+        <v>624</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>459</v>
+        <v>615</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>625</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>432</v>
+        <v>626</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>460</v>
+        <v>627</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>461</v>
+        <v>628</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>462</v>
+        <v>629</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>463</v>
+        <v>615</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>630</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>464</v>
+        <v>631</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>465</v>
+        <v>632</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>466</v>
+        <v>615</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>633</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>467</v>
+        <v>634</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>468</v>
+        <v>635</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="3"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>469</v>
+        <v>615</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>636</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>470</v>
+        <v>439</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>471</v>
+        <v>637</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>472</v>
+        <v>638</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>473</v>
+        <v>615</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>639</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>474</v>
+        <v>640</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>475</v>
+        <v>641</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>476</v>
+        <v>587</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>642</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>118</v>
+        <v>233</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>477</v>
+        <v>643</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>478</v>
+        <v>644</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>479</v>
+        <v>615</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>645</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>440</v>
+        <v>601</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>480</v>
+        <v>646</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>481</v>
+        <v>647</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -5978,9 +8080,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="13.75"/>
+    <col customWidth="1" min="2" max="2" width="19.38"/>
     <col customWidth="1" min="5" max="5" width="14.88"/>
-    <col customWidth="1" min="6" max="6" width="31.0"/>
+    <col customWidth="1" min="6" max="6" width="35.5"/>
     <col customWidth="1" min="7" max="7" width="21.25"/>
     <col customWidth="1" min="8" max="8" width="53.0"/>
     <col customWidth="1" min="9" max="9" width="43.88"/>
@@ -6018,741 +8120,948 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>483</v>
+        <v>659</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>660</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>484</v>
+        <v>661</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>485</v>
+        <v>662</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>486</v>
+        <v>663</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>487</v>
+        <v>659</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>664</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>488</v>
+        <v>665</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>489</v>
+        <v>666</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>490</v>
+        <v>659</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>667</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>491</v>
+        <v>668</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>492</v>
+        <v>669</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>493</v>
+        <v>659</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>670</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>494</v>
+        <v>592</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>495</v>
+        <v>671</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>496</v>
+        <v>672</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>497</v>
+        <v>659</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>673</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>498</v>
+        <v>674</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>499</v>
+        <v>675</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>501</v>
+        <v>676</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>677</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>502</v>
+        <v>678</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>503</v>
+        <v>676</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>679</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>504</v>
+        <v>680</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>505</v>
+        <v>681</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>506</v>
+        <v>682</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>507</v>
+        <v>683</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>508</v>
+        <v>659</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>684</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>509</v>
+        <v>685</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>510</v>
+        <v>686</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>511</v>
+        <v>687</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>512</v>
+        <v>659</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>688</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>513</v>
+        <v>434</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>514</v>
+        <v>689</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>515</v>
+        <v>659</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>690</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>516</v>
+        <v>691</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>517</v>
+        <v>692</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>518</v>
+        <v>659</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>693</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>519</v>
+        <v>694</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>520</v>
+        <v>695</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>521</v>
+        <v>659</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>696</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>522</v>
+        <v>697</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>523</v>
+        <v>698</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>524</v>
+        <v>659</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>699</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>525</v>
+        <v>700</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>526</v>
+        <v>676</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>701</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>527</v>
+        <v>702</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>528</v>
+        <v>703</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>529</v>
+        <v>659</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>704</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>530</v>
+        <v>366</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>531</v>
+        <v>705</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>532</v>
+        <v>676</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>706</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>533</v>
+        <v>707</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>534</v>
+        <v>708</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>535</v>
+        <v>709</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>536</v>
+        <v>659</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>710</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>537</v>
+        <v>711</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>538</v>
+        <v>712</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>539</v>
+        <v>659</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>713</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>540</v>
+        <v>714</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>541</v>
+        <v>715</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>542</v>
+        <v>676</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>716</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>543</v>
+        <v>461</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>544</v>
+        <v>717</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>545</v>
+        <v>718</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>546</v>
+        <v>676</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>719</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>547</v>
+        <v>720</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>548</v>
+        <v>721</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>549</v>
+        <v>659</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>722</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>550</v>
+        <v>592</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>551</v>
+        <v>723</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>552</v>
+        <v>659</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>724</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>553</v>
+        <v>725</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>554</v>
+        <v>676</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>726</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>555</v>
+        <v>649</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>556</v>
+        <v>727</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>557</v>
+        <v>728</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -6768,9 +9077,9 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="15.63"/>
-    <col customWidth="1" min="4" max="4" width="14.88"/>
-    <col customWidth="1" min="5" max="5" width="31.0"/>
-    <col customWidth="1" min="6" max="6" width="19.38"/>
+    <col customWidth="1" min="4" max="4" width="21.88"/>
+    <col customWidth="1" min="5" max="5" width="34.63"/>
+    <col customWidth="1" min="6" max="6" width="26.25"/>
     <col customWidth="1" min="7" max="7" width="72.38"/>
     <col customWidth="1" min="8" max="8" width="43.88"/>
     <col customWidth="1" min="9" max="9" width="17.38"/>
@@ -6804,210 +9113,302 @@
       <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
-      <c r="B2" s="2" t="s">
-        <v>558</v>
+      <c r="B2" s="3" t="s">
+        <v>745</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>559</v>
+        <v>746</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>560</v>
+        <v>747</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="s">
-        <v>561</v>
+      <c r="B3" s="3" t="s">
+        <v>748</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>562</v>
+        <v>749</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>563</v>
+        <v>750</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="2" t="s">
-        <v>564</v>
+      <c r="B4" s="3" t="s">
+        <v>751</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>565</v>
+        <v>752</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>566</v>
+        <v>753</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="s">
-        <v>567</v>
+      <c r="B5" s="3" t="s">
+        <v>754</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>568</v>
+        <v>755</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>569</v>
+        <v>756</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="2" t="s">
-        <v>570</v>
+      <c r="B6" s="3" t="s">
+        <v>757</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>571</v>
+        <v>758</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>572</v>
+        <v>759</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="2" t="s">
-        <v>573</v>
+      <c r="B7" s="3" t="s">
+        <v>760</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>574</v>
+        <v>761</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>575</v>
+        <v>762</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="s">
-        <v>576</v>
+      <c r="B8" s="3" t="s">
+        <v>763</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>577</v>
+        <v>764</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>578</v>
+        <v>765</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="2" t="s">
-        <v>579</v>
+      <c r="B9" s="3" t="s">
+        <v>766</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>580</v>
+        <v>767</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>581</v>
+        <v>768</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>
